--- a/doc/airsens_comm_erreurs.xlsx
+++ b/doc/airsens_comm_erreurs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f34ccaa6039d8a87/technique/_projets/esp32-micropython/esp32-airsens/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{7513B86E-3BFD-4976-A99D-C34F7B930E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5879C5C-1953-45B1-BDDF-F0213FB84B3B}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{7513B86E-3BFD-4976-A99D-C34F7B930E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA4FD08E-3E0A-4606-92C3-B97C3C9C66D4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30343E80-366C-4460-AF75-DAB25F03AC95}"/>
+    <workbookView xWindow="32130" yWindow="2580" windowWidth="21600" windowHeight="11055" xr2:uid="{30343E80-366C-4460-AF75-DAB25F03AC95}"/>
   </bookViews>
   <sheets>
     <sheet name="20220123" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="26">
   <si>
     <t>uC</t>
   </si>
@@ -97,6 +97,21 @@
   </si>
   <si>
     <t>erreurs %</t>
+  </si>
+  <si>
+    <t>COM5</t>
+  </si>
+  <si>
+    <t>jmb_06</t>
+  </si>
+  <si>
+    <t>jmb_05</t>
+  </si>
+  <si>
+    <t>no more T_WAIT_FOR_IRQ_TERMINATED_MS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jmb_05 --&gt; added 100uF on 3.3V </t>
   </si>
 </sst>
 </file>
@@ -106,7 +121,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,6 +130,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -143,12 +166,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886F255B-5E32-4FC2-80D5-E6E0217B3433}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="6" width="10.90625" style="1"/>
@@ -613,7 +639,301 @@
         <v>6.7114914425427871E-2</v>
       </c>
     </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1">
+        <v>7873</v>
+      </c>
+      <c r="F9" s="1">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2">
+        <f>F9/E9</f>
+        <v>1.2701638511367966E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="1">
+        <v>7019</v>
+      </c>
+      <c r="F10" s="1">
+        <v>89</v>
+      </c>
+      <c r="G10" s="2">
+        <f>F10/E10</f>
+        <v>1.2679868927197607E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1">
+        <v>7213</v>
+      </c>
+      <c r="F11" s="1">
+        <v>357</v>
+      </c>
+      <c r="G11" s="2">
+        <f>F11/E11</f>
+        <v>4.949396922223763E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="1">
+        <v>7980</v>
+      </c>
+      <c r="F12" s="1">
+        <v>602</v>
+      </c>
+      <c r="G12" s="2">
+        <f>F12/E12</f>
+        <v>7.5438596491228069E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4021</v>
+      </c>
+      <c r="F15" s="1">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2">
+        <f>F15/E15</f>
+        <v>7.4608306391444918E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3946</v>
+      </c>
+      <c r="F16" s="1">
+        <v>35</v>
+      </c>
+      <c r="G16" s="2">
+        <f>F16/E16</f>
+        <v>8.8697415103902687E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3957</v>
+      </c>
+      <c r="F17" s="1">
+        <v>28</v>
+      </c>
+      <c r="G17" s="2">
+        <f>F17/E17</f>
+        <v>7.0760677280768255E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="1">
+        <v>4187</v>
+      </c>
+      <c r="F18" s="1">
+        <v>170</v>
+      </c>
+      <c r="G18" s="2">
+        <f>F18/E18</f>
+        <v>4.0601862909004062E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="2" t="e">
+        <f>F21/E21</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="2" t="e">
+        <f>F22/E22</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="2" t="e">
+        <f>F23/E23</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="2" t="e">
+        <f>F24/E24</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:G12">
+    <sortCondition descending="1" ref="A9:A12"/>
+  </sortState>
+  <mergeCells count="2">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A20:G20"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/doc/airsens_comm_erreurs.xlsx
+++ b/doc/airsens_comm_erreurs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f34ccaa6039d8a87/technique/_projets/esp32-micropython/esp32-airsens/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{7513B86E-3BFD-4976-A99D-C34F7B930E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{413606B9-2738-478B-A70E-7B94435FDA4C}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="8_{7513B86E-3BFD-4976-A99D-C34F7B930E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F69E5830-80CB-4EFA-9460-40585DCFE2B3}"/>
   <bookViews>
-    <workbookView xWindow="32130" yWindow="2580" windowWidth="21600" windowHeight="11055" xr2:uid="{30343E80-366C-4460-AF75-DAB25F03AC95}"/>
+    <workbookView xWindow="32640" yWindow="3090" windowWidth="21600" windowHeight="11055" xr2:uid="{30343E80-366C-4460-AF75-DAB25F03AC95}"/>
   </bookViews>
   <sheets>
     <sheet name="20220204" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="30">
   <si>
     <t>uC</t>
   </si>
@@ -118,6 +118,12 @@
   </si>
   <si>
     <t>deepsleep 5 min</t>
+  </si>
+  <si>
+    <t>COM12</t>
+  </si>
+  <si>
+    <t>jmb_12</t>
   </si>
 </sst>
 </file>
@@ -172,19 +178,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886F255B-5E32-4FC2-80D5-E6E0217B3433}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -542,17 +551,17 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -708,14 +717,14 @@
       <c r="A9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
@@ -805,8 +814,8 @@
       <c r="E13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>8</v>
+      <c r="F13" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="I13" s="2" t="e">
         <f>H13/G13</f>
@@ -829,11 +838,35 @@
       <c r="E14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>8</v>
+      <c r="F14" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="I14" s="2" t="e">
         <f>H14/G14</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="2" t="e">
+        <f>H15/G15</f>
         <v>#DIV/0!</v>
       </c>
     </row>

--- a/doc/airsens_comm_erreurs.xlsx
+++ b/doc/airsens_comm_erreurs.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f34ccaa6039d8a87/technique/_projets/esp32-micropython/esp32-airsens/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{7513B86E-3BFD-4976-A99D-C34F7B930E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{413606B9-2738-478B-A70E-7B94435FDA4C}"/>
+  <xr:revisionPtr revIDLastSave="248" documentId="8_{7513B86E-3BFD-4976-A99D-C34F7B930E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC0E557E-A827-4F85-9679-AC5EFA98EED5}"/>
   <bookViews>
-    <workbookView xWindow="32130" yWindow="2580" windowWidth="21600" windowHeight="11055" xr2:uid="{30343E80-366C-4460-AF75-DAB25F03AC95}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{30343E80-366C-4460-AF75-DAB25F03AC95}"/>
   </bookViews>
   <sheets>
     <sheet name="20220204" sheetId="1" r:id="rId1"/>
+    <sheet name="20220207" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="59">
   <si>
     <t>uC</t>
   </si>
@@ -118,16 +119,110 @@
   </si>
   <si>
     <t>deepsleep 5 min</t>
+  </si>
+  <si>
+    <t>erreur</t>
+  </si>
+  <si>
+    <t>Write on BLE UART error [Errno 107] ENOTCONN</t>
+  </si>
+  <si>
+    <t>Write on BLE UART error -128</t>
+  </si>
+  <si>
+    <t>COM12</t>
+  </si>
+  <si>
+    <t>jmb_E2</t>
+  </si>
+  <si>
+    <t>jmb_E6</t>
+  </si>
+  <si>
+    <t>deepsleep 2 s</t>
+  </si>
+  <si>
+    <t>uPyton</t>
+  </si>
+  <si>
+    <t>v1.14</t>
+  </si>
+  <si>
+    <t>v1.15</t>
+  </si>
+  <si>
+    <t>v1.17</t>
+  </si>
+  <si>
+    <t>COM10</t>
+  </si>
+  <si>
+    <t>COM17</t>
+  </si>
+  <si>
+    <t>COM18</t>
+  </si>
+  <si>
+    <t>uC type</t>
+  </si>
+  <si>
+    <t>Port</t>
+  </si>
+  <si>
+    <t>uPython</t>
+  </si>
+  <si>
+    <t>Sensor</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>jmb_10</t>
+  </si>
+  <si>
+    <t>jmb_17</t>
+  </si>
+  <si>
+    <t>jmb_18</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>Passes</t>
+  </si>
+  <si>
+    <t>Erreurs</t>
+  </si>
+  <si>
+    <t>% erreur</t>
+  </si>
+  <si>
+    <t>Erreur description</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>USB2</t>
+  </si>
+  <si>
+    <t>USB3</t>
+  </si>
+  <si>
+    <t>Tous sur le même HUB - deepsleep 2s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,6 +245,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -159,7 +260,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -167,26 +268,71 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Milliers" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -500,348 +646,1170 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886F255B-5E32-4FC2-80D5-E6E0217B3433}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="7.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6328125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="7.6328125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="41.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="L1" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1">
         <v>13986</v>
       </c>
-      <c r="H3" s="1">
+      <c r="J3" s="1">
         <v>1744</v>
       </c>
-      <c r="I3" s="2">
-        <f>H3/G3</f>
+      <c r="K3" s="2">
+        <f>J3/I3</f>
         <v>0.12469612469612469</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="1">
         <v>14059</v>
       </c>
-      <c r="H4" s="1">
+      <c r="J4" s="1">
         <v>1409</v>
       </c>
-      <c r="I4" s="2">
-        <f>H4/G4</f>
+      <c r="K4" s="2">
+        <f>J4/I4</f>
         <v>0.10022049932427626</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="1">
         <v>16165</v>
       </c>
-      <c r="H5" s="1">
+      <c r="J5" s="1">
         <v>1113</v>
       </c>
-      <c r="I5" s="2">
-        <f>H5/G5</f>
+      <c r="K5" s="2">
+        <f>J5/I5</f>
         <v>6.8852459016393447E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>16036</v>
       </c>
-      <c r="H6" s="1">
+      <c r="J6" s="1">
         <v>558</v>
       </c>
-      <c r="I6" s="2">
-        <f>H6/G6</f>
+      <c r="K6" s="2">
+        <f>J6/I6</f>
         <v>3.4796707408331254E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="1">
         <v>13082</v>
       </c>
-      <c r="H7" s="1">
+      <c r="J7" s="1">
         <v>312</v>
       </c>
-      <c r="I7" s="2">
-        <f>H7/G7</f>
+      <c r="K7" s="2">
+        <f>J7/I7</f>
         <v>2.3849564286806298E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="2" t="e">
-        <f>H10/G10</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="1">
+        <v>155</v>
+      </c>
+      <c r="J10" s="1">
+        <v>15</v>
+      </c>
+      <c r="K10" s="2">
+        <f t="shared" ref="K10:K15" si="0">J10/I10</f>
+        <v>9.6774193548387094E-2</v>
+      </c>
+      <c r="L10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="2" t="e">
-        <f>H11/G11</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="1">
+        <v>192</v>
+      </c>
+      <c r="J11" s="1">
+        <v>51</v>
+      </c>
+      <c r="K11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.265625</v>
+      </c>
+      <c r="L11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="2" t="e">
-        <f>H12/G12</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="1">
+        <v>143</v>
+      </c>
+      <c r="J12" s="1">
+        <v>3</v>
+      </c>
+      <c r="K12" s="2">
+        <f t="shared" si="0"/>
+        <v>2.097902097902098E-2</v>
+      </c>
+      <c r="L12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" s="2" t="e">
-        <f>H13/G13</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="1">
+        <v>145</v>
+      </c>
+      <c r="J13" s="1">
+        <v>5</v>
+      </c>
+      <c r="K13" s="2">
+        <f t="shared" si="0"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="L13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="2" t="e">
-        <f>H14/G14</f>
-        <v>#DIV/0!</v>
+      <c r="G14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="1">
+        <v>140</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="1">
+        <v>147</v>
+      </c>
+      <c r="J15" s="1">
+        <v>6</v>
+      </c>
+      <c r="K15" s="2">
+        <f t="shared" si="0"/>
+        <v>4.0816326530612242E-2</v>
+      </c>
+      <c r="L15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="4">
+        <v>3370</v>
+      </c>
+      <c r="J18" s="4">
+        <v>185</v>
+      </c>
+      <c r="K18" s="2">
+        <f t="shared" ref="K18:K23" si="1">J18/I18</f>
+        <v>5.4896142433234422E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="4">
+        <v>3309</v>
+      </c>
+      <c r="J19" s="4">
+        <v>143</v>
+      </c>
+      <c r="K19" s="2">
+        <f t="shared" si="1"/>
+        <v>4.3215472952553645E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="4">
+        <v>3509</v>
+      </c>
+      <c r="J20" s="4">
+        <v>440</v>
+      </c>
+      <c r="K20" s="2">
+        <f t="shared" si="1"/>
+        <v>0.12539184952978055</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="4">
+        <v>3343</v>
+      </c>
+      <c r="J21" s="4">
+        <v>446</v>
+      </c>
+      <c r="K21" s="2">
+        <f t="shared" si="1"/>
+        <v>0.13341310200418785</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="4">
+        <v>3983</v>
+      </c>
+      <c r="J22" s="4">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2">
+        <f t="shared" si="1"/>
+        <v>2.0085362791865428E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="4">
+        <v>3263</v>
+      </c>
+      <c r="J23" s="4">
+        <v>329</v>
+      </c>
+      <c r="K23" s="2">
+        <f t="shared" si="1"/>
+        <v>0.10082745939319644</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="C24" s="7"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A9:I9"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A17:L17"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDF7D9D-49DD-4297-94A5-48F51916B2DB}">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="12">
+        <v>264</v>
+      </c>
+      <c r="J4" s="12">
+        <v>14</v>
+      </c>
+      <c r="K4" s="15">
+        <f>IF(I4&lt;&gt;"",J4/I4,"")</f>
+        <v>5.3030303030303032E-2</v>
+      </c>
+      <c r="L4" s="13"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="12">
+        <v>55</v>
+      </c>
+      <c r="J5" s="12">
+        <v>2</v>
+      </c>
+      <c r="K5" s="15">
+        <f t="shared" ref="K5:K9" si="0">IF(I5&lt;&gt;"",J5/I5,"")</f>
+        <v>3.6363636363636362E-2</v>
+      </c>
+      <c r="L5" s="13"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="12">
+        <v>232</v>
+      </c>
+      <c r="J6" s="12">
+        <v>27</v>
+      </c>
+      <c r="K6" s="15">
+        <f t="shared" si="0"/>
+        <v>0.11637931034482758</v>
+      </c>
+      <c r="L6" s="13"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="12">
+        <v>18</v>
+      </c>
+      <c r="J7" s="12">
+        <v>2</v>
+      </c>
+      <c r="K7" s="15">
+        <f t="shared" si="0"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="L7" s="13"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="12">
+        <v>219</v>
+      </c>
+      <c r="J8" s="12">
+        <v>34</v>
+      </c>
+      <c r="K8" s="15">
+        <f t="shared" si="0"/>
+        <v>0.15525114155251141</v>
+      </c>
+      <c r="L8" s="13"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="12">
+        <v>241</v>
+      </c>
+      <c r="J9" s="12">
+        <v>24</v>
+      </c>
+      <c r="K9" s="15">
+        <f t="shared" si="0"/>
+        <v>9.9585062240663894E-2</v>
+      </c>
+      <c r="L9" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:L3"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
